--- a/artfynd/Vitstensberget artfynd.xlsx
+++ b/artfynd/Vitstensberget artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16944859</v>
+        <v>16944436</v>
       </c>
       <c r="B2" t="n">
-        <v>79987</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699105</v>
+        <v>698210</v>
       </c>
       <c r="R2" t="n">
-        <v>7097213</v>
+        <v>7096796</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56606367</v>
+        <v>16945115</v>
       </c>
       <c r="B3" t="n">
-        <v>82792</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698695</v>
+        <v>698547</v>
       </c>
       <c r="R3" t="n">
-        <v>7097484</v>
+        <v>7096675</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16944675</v>
+        <v>54066397</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698437</v>
+        <v>698420</v>
       </c>
       <c r="R4" t="n">
-        <v>7096700</v>
+        <v>7097103</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,17 +978,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -996,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54066371</v>
+        <v>16944437</v>
       </c>
       <c r="B5" t="n">
-        <v>90629</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5685</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698706</v>
+        <v>698868</v>
       </c>
       <c r="R5" t="n">
-        <v>7097116</v>
+        <v>7097096</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,22 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,17 +1090,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16944483</v>
+        <v>54066365</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698376</v>
+        <v>698397</v>
       </c>
       <c r="R6" t="n">
-        <v>7096870</v>
+        <v>7096934</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,17 +1212,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54066382</v>
+        <v>54066393</v>
       </c>
       <c r="B7" t="n">
-        <v>80084</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698692</v>
+        <v>698606</v>
       </c>
       <c r="R7" t="n">
-        <v>7096610</v>
+        <v>7096650</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1300,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,17 +1334,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56606366</v>
+        <v>54066394</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698672</v>
+        <v>698514</v>
       </c>
       <c r="R8" t="n">
-        <v>7097528</v>
+        <v>7096689</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,12 +1427,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,48 +1453,63 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54066384</v>
+        <v>16944927</v>
       </c>
       <c r="B9" t="n">
-        <v>91195</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1519,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699008</v>
+        <v>698694</v>
       </c>
       <c r="R9" t="n">
-        <v>7097081</v>
+        <v>7096750</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,22 +1549,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,17 +1568,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1574,7 +1599,7 @@
         <v>54066366</v>
       </c>
       <c r="B10" t="n">
-        <v>82792</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54066401</v>
+        <v>54066367</v>
       </c>
       <c r="B11" t="n">
-        <v>56840</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,43 +1729,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698420</v>
+        <v>698423</v>
       </c>
       <c r="R11" t="n">
-        <v>7097103</v>
+        <v>7097108</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,6 +1809,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1809,32 +1840,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>54066361</v>
+        <v>54066382</v>
       </c>
       <c r="B12" t="n">
-        <v>80118</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698577</v>
+        <v>698692</v>
       </c>
       <c r="R12" t="n">
-        <v>7097171</v>
+        <v>7096610</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16944407</v>
+        <v>54066380</v>
       </c>
       <c r="B13" t="n">
-        <v>80118</v>
+        <v>96350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,21 +1973,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>2813</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,13 +1997,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698956</v>
+        <v>698680</v>
       </c>
       <c r="R13" t="n">
-        <v>7097107</v>
+        <v>7096608</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,12 +2027,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,21 +2053,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2043,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54066381</v>
+        <v>54066363</v>
       </c>
       <c r="B14" t="n">
-        <v>98279</v>
+        <v>91966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,21 +2080,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>5321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698676</v>
+        <v>698516</v>
       </c>
       <c r="R14" t="n">
-        <v>7096614</v>
+        <v>7096676</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,6 +2160,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2150,32 +2191,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56606369</v>
+        <v>54066371</v>
       </c>
       <c r="B15" t="n">
-        <v>79012</v>
+        <v>91282</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>5685</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,13 +2226,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698722</v>
+        <v>698706</v>
       </c>
       <c r="R15" t="n">
-        <v>7097436</v>
+        <v>7097116</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,12 +2256,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,48 +2282,63 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16944463</v>
+        <v>54066378</v>
       </c>
       <c r="B16" t="n">
-        <v>91506</v>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,13 +2348,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698931</v>
+        <v>698638</v>
       </c>
       <c r="R16" t="n">
-        <v>7097112</v>
+        <v>7097092</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,12 +2378,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,22 +2407,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>låga</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # låga</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2364,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118697221</v>
+        <v>16944669</v>
       </c>
       <c r="B17" t="n">
-        <v>57307</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,51 +2446,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100063</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitstenberget, Ång</t>
+          <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698936</v>
+        <v>698505</v>
       </c>
       <c r="R17" t="n">
-        <v>7097479</v>
+        <v>7096690</v>
       </c>
       <c r="S17" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,27 +2500,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Över berget, kacklande, trolig pendling mellan häckningstjärn och fiskesjö</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,26 +2516,41 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>54066397</v>
+        <v>16944675</v>
       </c>
       <c r="B18" t="n">
-        <v>88654</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,21 +2558,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,13 +2582,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698420</v>
+        <v>698437</v>
       </c>
       <c r="R18" t="n">
-        <v>7097103</v>
+        <v>7096700</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,22 +2612,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,17 +2631,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2612,32 +2659,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54066362</v>
+        <v>54066374</v>
       </c>
       <c r="B19" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2647,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698577</v>
+        <v>698614</v>
       </c>
       <c r="R19" t="n">
-        <v>7097171</v>
+        <v>7096636</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2682,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,17 +2753,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2734,10 +2781,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54066378</v>
+        <v>54066362</v>
       </c>
       <c r="B20" t="n">
-        <v>79987</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2745,21 +2792,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,10 +2816,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698638</v>
+        <v>698577</v>
       </c>
       <c r="R20" t="n">
-        <v>7097092</v>
+        <v>7097171</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2861,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,17 +2875,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2856,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16944606</v>
+        <v>54066383</v>
       </c>
       <c r="B21" t="n">
-        <v>80119</v>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,21 +2914,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2891,13 +2938,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698956</v>
+        <v>698692</v>
       </c>
       <c r="R21" t="n">
-        <v>7097107</v>
+        <v>7096610</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2921,12 +2968,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16944408</v>
+        <v>54066361</v>
       </c>
       <c r="B22" t="n">
-        <v>80118</v>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,13 +3060,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698953</v>
+        <v>698577</v>
       </c>
       <c r="R22" t="n">
-        <v>7097239</v>
+        <v>7097171</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3033,12 +3090,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,45 +3147,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>54066394</v>
+        <v>54066398</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698514</v>
+        <v>698420</v>
       </c>
       <c r="R23" t="n">
-        <v>7096689</v>
+        <v>7097103</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3150,7 +3226,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3160,7 +3236,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,21 +3247,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3202,45 +3263,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>54066374</v>
+        <v>54066401</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>57132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698614</v>
+        <v>698420</v>
       </c>
       <c r="R24" t="n">
-        <v>7096636</v>
+        <v>7097103</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3272,7 +3342,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3352,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,21 +3363,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3324,10 +3379,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16944951</v>
+        <v>54066402</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>57144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,37 +3390,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698953</v>
+        <v>698420</v>
       </c>
       <c r="R25" t="n">
-        <v>7097239</v>
+        <v>7097103</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3389,12 +3448,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,21 +3474,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3436,32 +3490,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16944669</v>
+        <v>54066376</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>98186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3471,13 +3525,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698505</v>
+        <v>698681</v>
       </c>
       <c r="R26" t="n">
-        <v>7096690</v>
+        <v>7096599</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3501,12 +3555,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,21 +3581,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3548,32 +3597,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>54066365</v>
+        <v>54066381</v>
       </c>
       <c r="B27" t="n">
-        <v>91819</v>
+        <v>99036</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>223591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3583,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698397</v>
+        <v>698676</v>
       </c>
       <c r="R27" t="n">
-        <v>7096934</v>
+        <v>7096614</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3618,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3628,7 +3677,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,21 +3688,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3670,10 +3704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16944894</v>
+        <v>56606368</v>
       </c>
       <c r="B28" t="n">
-        <v>80084</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,21 +3715,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3705,13 +3739,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698953</v>
+        <v>698715</v>
       </c>
       <c r="R28" t="n">
-        <v>7097239</v>
+        <v>7097824</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3751,63 +3785,48 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>54066376</v>
+        <v>56606369</v>
       </c>
       <c r="B29" t="n">
-        <v>97437</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220250</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3817,13 +3836,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698681</v>
+        <v>698722</v>
       </c>
       <c r="R29" t="n">
-        <v>7096599</v>
+        <v>7097436</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3847,22 +3866,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>06:54</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>06:54</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,44 +3886,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16944437</v>
+        <v>56606366</v>
       </c>
       <c r="B30" t="n">
-        <v>91819</v>
+        <v>92208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3924,13 +3933,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698868</v>
+        <v>698672</v>
       </c>
       <c r="R30" t="n">
-        <v>7097096</v>
+        <v>7097528</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3970,41 +3979,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>54066393</v>
+        <v>56606367</v>
       </c>
       <c r="B31" t="n">
-        <v>91245</v>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4012,21 +4006,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4036,13 +4030,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698606</v>
+        <v>698695</v>
       </c>
       <c r="R31" t="n">
-        <v>7096650</v>
+        <v>7097484</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4066,22 +4060,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>07:13</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>07:13</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,83 +4076,64 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>54066402</v>
+        <v>16944463</v>
       </c>
       <c r="B32" t="n">
-        <v>56852</v>
+        <v>92183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102613</v>
+        <v>65</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698420</v>
+        <v>698931</v>
       </c>
       <c r="R32" t="n">
-        <v>7097103</v>
+        <v>7097112</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,22 +4157,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4218,6 +4173,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # låga</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4234,10 +4209,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16944672</v>
+        <v>54066384</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>91859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4245,21 +4220,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4269,13 +4244,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>698956</v>
+        <v>699008</v>
       </c>
       <c r="R33" t="n">
-        <v>7097107</v>
+        <v>7097081</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4299,12 +4274,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4318,17 +4303,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4346,10 +4331,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16944676</v>
+        <v>16944894</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,21 +4342,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4458,32 +4443,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16945115</v>
+        <v>16944859</v>
       </c>
       <c r="B35" t="n">
-        <v>79012</v>
+        <v>80336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4493,10 +4478,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>698547</v>
+        <v>699105</v>
       </c>
       <c r="R35" t="n">
-        <v>7096675</v>
+        <v>7097213</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4539,6 +4524,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4555,32 +4555,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16944927</v>
+        <v>16944672</v>
       </c>
       <c r="B36" t="n">
-        <v>91256</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>698694</v>
+        <v>698956</v>
       </c>
       <c r="R36" t="n">
-        <v>7096750</v>
+        <v>7097107</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4639,17 +4639,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>54066370</v>
+        <v>16944676</v>
       </c>
       <c r="B37" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>698534</v>
+        <v>698953</v>
       </c>
       <c r="R37" t="n">
-        <v>7096670</v>
+        <v>7097239</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4732,22 +4732,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:31</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:31</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4761,17 +4751,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4789,10 +4779,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>54066363</v>
+        <v>16944951</v>
       </c>
       <c r="B38" t="n">
-        <v>91298</v>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,21 +4790,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5321</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4824,13 +4814,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>698516</v>
+        <v>698953</v>
       </c>
       <c r="R38" t="n">
-        <v>7096676</v>
+        <v>7097239</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4854,22 +4844,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>07:40</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>07:40</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,17 +4863,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4911,10 +4891,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>54066398</v>
+        <v>16944952</v>
       </c>
       <c r="B39" t="n">
-        <v>56849</v>
+        <v>80461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4922,46 +4902,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>698420</v>
+        <v>699129</v>
       </c>
       <c r="R39" t="n">
-        <v>7097103</v>
+        <v>7097193</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4985,22 +4956,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5011,6 +4972,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5027,32 +5003,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>54066367</v>
+        <v>16944407</v>
       </c>
       <c r="B40" t="n">
-        <v>82792</v>
+        <v>80467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5062,13 +5038,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>698423</v>
+        <v>698956</v>
       </c>
       <c r="R40" t="n">
-        <v>7097108</v>
+        <v>7097107</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5092,22 +5068,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>08:43</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>08:43</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5121,17 +5087,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5149,51 +5115,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>81775661</v>
+        <v>16944408</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>80467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Balberget, Ång</t>
+          <t>Vitstensberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>698923</v>
+        <v>698953</v>
       </c>
       <c r="R41" t="n">
-        <v>7097466</v>
+        <v>7097239</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5217,12 +5180,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5231,51 +5194,65 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kerstin Årdahl</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kerstin Årdahl</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16944436</v>
+        <v>16944606</v>
       </c>
       <c r="B42" t="n">
-        <v>91819</v>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5285,10 +5262,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698210</v>
+        <v>698956</v>
       </c>
       <c r="R42" t="n">
-        <v>7096796</v>
+        <v>7097107</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5362,48 +5339,51 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>54066380</v>
+        <v>81775661</v>
       </c>
       <c r="B43" t="n">
-        <v>95606</v>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vitstensberget, Ång</t>
+          <t>Balberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698680</v>
+        <v>698923</v>
       </c>
       <c r="R43" t="n">
-        <v>7096608</v>
+        <v>7097466</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5427,22 +5407,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>06:57</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>06:57</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5451,28 +5421,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Kerstin Årdahl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Kerstin Årdahl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>54066383</v>
+        <v>118697221</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>57602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5480,37 +5451,51 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>100063</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vitstensberget, Ång</t>
+          <t>Vitstenberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>698692</v>
+        <v>698936</v>
       </c>
       <c r="R44" t="n">
-        <v>7096610</v>
+        <v>7097479</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5534,22 +5519,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Över berget, kacklande, trolig pendling mellan häckningstjärn och fiskesjö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5560,31 +5550,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Anders Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Anders Enetjärn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
